--- a/Cardiologie/Excel/cardio_1.xlsx
+++ b/Cardiologie/Excel/cardio_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Haris\Site-Web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBDE55D-B5B6-4672-8DCC-C0760A722C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B5C3B-7FA9-4096-924C-D2C61041CFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,16 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="105">
-  <si>
-    <t>numero</t>
-  </si>
-  <si>
-    <t>proposition</t>
-  </si>
-  <si>
-    <t>reponse</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>L'athérosclérose affecte uniformément toutes les artères.</t>
   </si>
@@ -331,26 +322,33 @@
     <t>Un risque moyen de décès cardiovasculaire correspond à &lt;1% de mortalité à 10 ans en l’absence de traitement.</t>
   </si>
   <si>
-    <t>Faux</t>
-  </si>
-  <si>
-    <t>Vrai</t>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>Proposition</t>
+  </si>
+  <si>
+    <t>Reponse</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -366,7 +364,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -374,32 +372,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -705,1130 +691,1144 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="202.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="202.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E11" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="D14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E14" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E15" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E17" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="D18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E18" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E19" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E20" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E21" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E22" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E23" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="D24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="D25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E25" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="D26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E26" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="D27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E27" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="D28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E28" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E29" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E30" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="D31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E31" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="D32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E32" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="D33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E33" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="D34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E34" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="D35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E35" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="D36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E36" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="D37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E37" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="D38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E38" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="D39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E39" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="D40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E40" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="D41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E41" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="D42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E42" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="D43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E43" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="D44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E44" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="D45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E45" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="D46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E46" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="D47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E47" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="D48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E48" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="D49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E49" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="D50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E50" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="D51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E51" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="D52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E52" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="D53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E53" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="D54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E54" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="D55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E55" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="D56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E56" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="D57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E57" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="D58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E58" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="D59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E59" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="D60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E60" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="D61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E61" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="D62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E62" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="D63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E63" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="D64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="E64" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="D65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E65" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="D66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E66" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="D67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E67" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="D68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E68" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="D69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="E69" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="D70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E70" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="D71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E71" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="D72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E72" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="D73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="E73" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="D74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E74" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="D75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E75" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="D76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="E76" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="D77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="E77" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="D78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="E78" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="D79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="E79" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="D80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E80" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="D81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="E81" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="D82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E82" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="D83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="E83" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="D84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="E84" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="D85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="E85" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="D86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="E86" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="D87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="E87" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="D88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="E88" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="D89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E89" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="D90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="E90" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="D91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="E91" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="D92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="E92" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="D93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="E93" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="D94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="E94" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="D95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="E95" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="D96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="E96" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="D97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E97" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="D98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="E98" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="D99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="E99" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="D100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="E100" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="D101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>100</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>103</v>
+      <c r="E101" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Cardiologie/Excel/cardio_1.xlsx
+++ b/Cardiologie/Excel/cardio_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Haris\Site-Web\Cardiologie\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B5C3B-7FA9-4096-924C-D2C61041CFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF2A34D-1326-446C-B129-E3FFD18AA682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -376,12 +376,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -695,46 +692,44 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="202.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.5703125" style="1"/>
+    <col min="2" max="2" width="202.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="b">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -742,10 +737,10 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="b">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -753,10 +748,10 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="b">
+      <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -764,10 +759,10 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="2" t="b">
+      <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -775,10 +770,10 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="b">
+      <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -786,10 +781,10 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -797,10 +792,10 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="2" t="b">
+      <c r="C8" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -808,10 +803,10 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="C9" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -819,10 +814,10 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="2" t="b">
+      <c r="C10" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -830,10 +825,10 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="2" t="b">
+      <c r="C11" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -841,10 +836,10 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="2" t="b">
+      <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -852,10 +847,10 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="b">
+      <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -863,10 +858,10 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="2" t="b">
+      <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -874,10 +869,10 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="2" t="b">
+      <c r="C15" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -885,945 +880,945 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C29" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C31" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C34" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C37" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E40" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C40" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C41" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E42" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C43" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E44" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C44" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E45" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C45" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E46" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E48" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E49" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C49" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E50" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C50" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E51" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C51" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E52" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C52" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E53" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E54" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C54" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E55" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C55" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E57" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C57" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E58" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E59" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C59" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E60" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E61" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C61" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E62" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E63" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E64" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C64" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E65" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E66" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C66" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C67" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E68" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E69" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C69" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E70" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C70" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C71" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E72" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C72" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E73" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C73" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E74" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C74" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E75" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C75" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C76" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E77" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C77" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E78" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C78" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E79" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C79" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E80" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C80" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E81" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C81" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E82" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E83" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C83" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E84" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C84" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E85" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C85" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E86" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C86" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E87" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C87" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E88" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C88" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E89" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C89" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E90" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E91" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E92" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C92" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E93" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C93" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E94" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C94" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E95" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C95" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E96" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C96" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E97" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C97" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E98" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C98" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E99" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C99" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E100" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C100" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E101" s="2" t="b">
+      <c r="C101" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Cardiologie/Excel/cardio_1.xlsx
+++ b/Cardiologie/Excel/cardio_1.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Haris\Site-Web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF2A34D-1326-446C-B129-E3FFD18AA682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1644A1-2324-469D-A967-645B675B0B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="145">
   <si>
     <t>L'athérosclérose affecte uniformément toutes les artères.</t>
   </si>
@@ -169,18 +182,9 @@
     <t>Un BMI supérieur à 25 kg/m² est associé à un risque accru de maladie cardiovasculaire.</t>
   </si>
   <si>
-    <t>Une circonférence abdominale supérieure à 95cm chez la femme n’est pas un facteur de risque cardiovasculaire.</t>
-  </si>
-  <si>
-    <t>Les patients ayant présenté un AIT doivent faire l’objet d’une prévention secondaire.</t>
-  </si>
-  <si>
     <t>Des triglycérides à 120mg/dl dans le sang n’augmentent pas le risque cardiovasculaire.</t>
   </si>
   <si>
-    <t>Une PAD supérieure à 110mmHg est considérée comme une HTA de grade</t>
-  </si>
-  <si>
     <t>Une réduction de cholestérol total de 2% réduit les évènements coronariens de 1%.</t>
   </si>
   <si>
@@ -232,9 +236,6 @@
     <t>Les fibroblastes ne jouent aucun rôle dans la formation de la plaque athéromateuse.</t>
   </si>
   <si>
-    <t>Les maladies cardiovasculaires sont la 2ème cause de décès en Belgique, juste derrière les cancers.</t>
-  </si>
-  <si>
     <t>La migration des cellules musculaires lisses amincit la média dans l’athéromatose.</t>
   </si>
   <si>
@@ -289,12 +290,6 @@
     <t>L’âge supérieur à 55 ans est un facteur de risque cardiovasculaire chez la femme.</t>
   </si>
   <si>
-    <t>Le LDL-cholestérol doit être inférieur à 115 mg/L.</t>
-  </si>
-  <si>
-    <t>Les femmes ont un taux de HDL-cholestérol naturellement plus élevé.</t>
-  </si>
-  <si>
     <t>Les facteurs de risque cardiovasculaires cumulés ont un effet multiplicatif sur le risque global.</t>
   </si>
   <si>
@@ -310,9 +305,6 @@
     <t>Pour convertir le risque cardiovasculaire fatal en risque cardiovasculaire total (fatal et non fatal), il faut multiplier le risque obtenu par la table SCORE par 3 chez les femmes et par 4 chez les hommes (moins chez le sujet âgé).</t>
   </si>
   <si>
-    <t>La table SCORE peut être utilisée chez les sujets diabétique car elle prend en compte le taux de glucose à jeun.</t>
-  </si>
-  <si>
     <t>L’arrêt du tabac entraine une disparition de l’excès de risque cardiovasculaire après 3-4 ans.</t>
   </si>
   <si>
@@ -341,6 +333,141 @@
   </si>
   <si>
     <t>Reference</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Elles se transforment en fibroblastes</t>
+  </si>
+  <si>
+    <t>Ce sont les symptömes cliniques de l'angor stable</t>
+  </si>
+  <si>
+    <t>Il est secreté  par l'endothélium</t>
+  </si>
+  <si>
+    <t>surface non-adhérente</t>
+  </si>
+  <si>
+    <t>C'est dans celui de type II</t>
+  </si>
+  <si>
+    <t>C'est dans celui de type III</t>
+  </si>
+  <si>
+    <t>de lipides extracellulaires</t>
+  </si>
+  <si>
+    <t>C'est le type V</t>
+  </si>
+  <si>
+    <t>Contient principalement du collagène</t>
+  </si>
+  <si>
+    <t>Plus fréquent</t>
+  </si>
+  <si>
+    <t>Ne diminue pas</t>
+  </si>
+  <si>
+    <t>De 75%</t>
+  </si>
+  <si>
+    <t>Produite par les cellules endothéliales</t>
+  </si>
+  <si>
+    <t>Non il y a des risques non modifiables</t>
+  </si>
+  <si>
+    <t>non modifiable</t>
+  </si>
+  <si>
+    <t>poids / taille au carré</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>ça réduit par rapport</t>
+  </si>
+  <si>
+    <t>de 0,9mm</t>
+  </si>
+  <si>
+    <t>30-60ml/min/1,73m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supérieur à </t>
+  </si>
+  <si>
+    <t>augmenté</t>
+  </si>
+  <si>
+    <t>supérieur à 30</t>
+  </si>
+  <si>
+    <t>Une PAD supérieure à 110mmHg est considérée comme une HTA de grade 3</t>
+  </si>
+  <si>
+    <t>c'est l'inverse, réduire de 1% diminue de 2%</t>
+  </si>
+  <si>
+    <t>140 et 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supérieur à </t>
+  </si>
+  <si>
+    <t>c'est chez les patients à risque élevé</t>
+  </si>
+  <si>
+    <t>Pas que ça</t>
+  </si>
+  <si>
+    <t>Une fois par an</t>
+  </si>
+  <si>
+    <t>D'abord l'intima</t>
+  </si>
+  <si>
+    <t>Que en prévention primaire</t>
+  </si>
+  <si>
+    <t>Que à partir du type 5 que la lumiere se réduit et que les symptomes apparaissent</t>
+  </si>
+  <si>
+    <t>Ca peut aussi toucher l'aorte</t>
+  </si>
+  <si>
+    <t>jsp ça sort d’où l'artere mammaire interne mais ok</t>
+  </si>
+  <si>
+    <t>C'est eux qui produisent la matrice extracellulaire qui va se transformer en plaque</t>
+  </si>
+  <si>
+    <t>si, ça peut etre prononcée</t>
+  </si>
+  <si>
+    <t>C'est là où c'est épaissie que c'est préférentiel</t>
+  </si>
+  <si>
+    <t>C'est des macrophages</t>
+  </si>
+  <si>
+    <t>pas encore</t>
+  </si>
+  <si>
+    <t>c'est dans le type 6</t>
+  </si>
+  <si>
+    <t>Chez l'homme</t>
+  </si>
+  <si>
+    <t>3 chez les hommes et 4 chez les femmes</t>
+  </si>
+  <si>
+    <t>C'est risque faible</t>
   </si>
 </sst>
 </file>
@@ -376,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -384,6 +511,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,1138 +819,1766 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="202.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="19.5703125" style="4"/>
+    <col min="2" max="2" width="70.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="4"/>
+    <col min="4" max="4" width="39.5703125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="19.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>100</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="C2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="C3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="C4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="C5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="C6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="C7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="b">
-        <v>0</v>
+      <c r="C8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="b">
-        <v>0</v>
+      <c r="C9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="b">
-        <v>0</v>
+      <c r="C10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="C11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="C12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="C13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="C14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="C15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="C16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="C17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="C18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="C19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="C20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="C21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="C22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="C23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="C24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="C25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="C26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="C27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="C28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="C29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="C30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="C31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="C32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="C33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="C34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="C35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="C36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="C37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="C38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="C39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="C40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="C41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="C42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="C43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="C44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="C45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="C46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="C47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="C48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="C49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="C50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="C51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="C53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="C55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="C56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="C57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="C58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C57" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="C59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="C60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C59" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="C61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="C62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+      <c r="C63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="C64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="C65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C64" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="C66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="C67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="C68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="C69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C68" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+      <c r="C70" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C69" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+      <c r="C71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C70" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="C72" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C71" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+      <c r="C73" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+      <c r="C74" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+      <c r="C75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="4">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+      <c r="C76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+      <c r="C77" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="4">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+      <c r="C78" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+      <c r="C79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C78" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+      <c r="C80" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C79" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+      <c r="C81" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="C82" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+      <c r="C83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+      <c r="C84" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C83" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+      <c r="C85" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C84" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="C86" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="C87" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C86" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+      <c r="C88" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C87" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+      <c r="C89" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C88" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
+      <c r="C90" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+      <c r="C91" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C90" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+      <c r="C92" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C91" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+      <c r="C93" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C92" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="C94" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C93" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>93</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C94" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>94</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>95</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>96</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C97" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>97</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C98" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>98</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C99" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>99</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C100" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>100</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C101" s="1" t="b">
-        <v>0</v>
+      <c r="C95" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
